--- a/SQLQry7T.xlsx
+++ b/SQLQry7T.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\JobLPst\CSVFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA31FD0F-1835-4E11-8984-EA61DB6138EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CA53C5-356C-4ACE-92FD-73D6A656E91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C5D5E17-7C89-41B3-BB89-71C3A719D0F3}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Freight Transport Carrier</t>
   </si>
   <si>
-    <t>Global Theater</t>
-  </si>
-  <si>
     <t>Allocated Node CapEx (USD)</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>Canada</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -773,18 +773,6 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -934,6 +922,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -941,18 +938,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -969,17 +969,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E815BE9F-8540-4531-869B-617DF4730580}" name="Table1" displayName="Table1" ref="A1:H6" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E815BE9F-8540-4531-869B-617DF4730580}" name="Table1" displayName="Table1" ref="A1:H6" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:H6" xr:uid="{E815BE9F-8540-4531-869B-617DF4730580}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8C12FD7D-CAF2-4021-B038-B1C841470DD6}" name="Origin Logistics Hub" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{C54D9162-368E-41D5-85B6-C7D02BAD7481}" name="Distribution Zone" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{D9823F4A-ED7E-409F-9769-4737B40ECE29}" name="Freight Transport Carrier" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{AD626E66-36C5-4A33-A9A4-4DDA24E22A48}" name="Pallets Ingested " dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{7BC399FE-3EDE-4A11-BD63-993BACD339FA}" name="Target Manufacturing Tenant" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{C075E2CB-2F62-49F4-A5DB-EAAFD553EA80}" name="Global Theater" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{8B8CCCF8-469D-42B8-ADF4-3FCCEF1A7F83}" name="Allocated Node CapEx (USD)" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{7943BBBB-F180-4B79-9BA6-6C9A66130AC8}" name="Site System Status" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8C12FD7D-CAF2-4021-B038-B1C841470DD6}" name="Origin Logistics Hub" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C54D9162-368E-41D5-85B6-C7D02BAD7481}" name="Distribution Zone" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{D9823F4A-ED7E-409F-9769-4737B40ECE29}" name="Freight Transport Carrier" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{AD626E66-36C5-4A33-A9A4-4DDA24E22A48}" name="Pallets Ingested " dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{7BC399FE-3EDE-4A11-BD63-993BACD339FA}" name="Target Manufacturing Tenant" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{C075E2CB-2F62-49F4-A5DB-EAAFD553EA80}" name="Region" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{8B8CCCF8-469D-42B8-ADF4-3FCCEF1A7F83}" name="Allocated Node CapEx (USD)" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{7943BBBB-F180-4B79-9BA6-6C9A66130AC8}" name="Site System Status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1327,149 +1327,149 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="F1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="1">
         <v>64</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="2">
         <v>106000000</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D3" s="1">
         <v>52</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="G3" s="2">
         <v>122000000</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="1">
         <v>48</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="G4" s="2">
         <v>132000000</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D5" s="1">
         <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2">
         <v>118000000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="D6" s="9">
         <v>36</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="G6" s="10">
         <v>115000000</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">

--- a/SQLQry7T.xlsx
+++ b/SQLQry7T.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CA53C5-356C-4ACE-92FD-73D6A656E91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0517D623-2301-4757-BE90-FE68009DC75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C5D5E17-7C89-41B3-BB89-71C3A719D0F3}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t xml:space="preserve">Pallets Ingested </t>
   </si>
   <si>
-    <t>Target Manufacturing Tenant</t>
-  </si>
-  <si>
     <t>China</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>Command Tier</t>
   </si>
 </sst>
 </file>
@@ -976,7 +976,7 @@
     <tableColumn id="2" xr3:uid="{C54D9162-368E-41D5-85B6-C7D02BAD7481}" name="Distribution Zone" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{D9823F4A-ED7E-409F-9769-4737B40ECE29}" name="Freight Transport Carrier" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{AD626E66-36C5-4A33-A9A4-4DDA24E22A48}" name="Pallets Ingested " dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{7BC399FE-3EDE-4A11-BD63-993BACD339FA}" name="Target Manufacturing Tenant" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{7BC399FE-3EDE-4A11-BD63-993BACD339FA}" name="Command Tier" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{C075E2CB-2F62-49F4-A5DB-EAAFD553EA80}" name="Region" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{8B8CCCF8-469D-42B8-ADF4-3FCCEF1A7F83}" name="Allocated Node CapEx (USD)" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{7943BBBB-F180-4B79-9BA6-6C9A66130AC8}" name="Site System Status" dataDxfId="0"/>
@@ -1330,10 +1330,10 @@
         <v>9</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>3</v>
@@ -1359,117 +1359,117 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2">
         <v>106000000</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="1">
         <v>52</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="G3" s="2">
         <v>122000000</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D4" s="1">
         <v>48</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="G4" s="2">
         <v>132000000</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D5" s="1">
         <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2">
         <v>118000000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="D6" s="9">
         <v>36</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="G6" s="10">
         <v>115000000</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
